--- a/exports/amazon-avaliacoes-budamix-2026-05-12.xlsx
+++ b/exports/amazon-avaliacoes-budamix-2026-05-12.xlsx
@@ -83,7 +83,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -102,6 +102,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00D9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -179,9 +186,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaResumoASINs" displayName="TabelaResumoASINs" ref="A1:R45" headerRowCount="1">
-  <autoFilter ref="A1:R45"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaResumoASINs" displayName="TabelaResumoASINs" ref="A1:T45" headerRowCount="1">
+  <autoFilter ref="A1:T45"/>
+  <tableColumns count="20">
     <tableColumn id="1" name="ASIN"/>
     <tableColumn id="2" name="SKU Base"/>
     <tableColumn id="3" name="SKU Anúncio"/>
@@ -192,38 +199,43 @@
     <tableColumn id="8" name="Total Classificações"/>
     <tableColumn id="9" name="Avaliações Escritas Públicas"/>
     <tableColumn id="10" name="Reviews Extraídas"/>
-    <tableColumn id="11" name="5 estrelas"/>
-    <tableColumn id="12" name="4 estrelas"/>
-    <tableColumn id="13" name="3 estrelas"/>
-    <tableColumn id="14" name="2 estrelas"/>
-    <tableColumn id="15" name="1 estrela"/>
-    <tableColumn id="16" name="Status Página"/>
-    <tableColumn id="17" name="Status URL Reviews"/>
-    <tableColumn id="18" name="URL Produto"/>
+    <tableColumn id="11" name="Nomes Válidos Extraídos"/>
+    <tableColumn id="12" name="Nomes Inválidos Filtrados"/>
+    <tableColumn id="13" name="5 estrelas"/>
+    <tableColumn id="14" name="4 estrelas"/>
+    <tableColumn id="15" name="3 estrelas"/>
+    <tableColumn id="16" name="2 estrelas"/>
+    <tableColumn id="17" name="1 estrela"/>
+    <tableColumn id="18" name="Status Página"/>
+    <tableColumn id="19" name="Status URL Reviews"/>
+    <tableColumn id="20" name="URL Produto"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TabelaReviewsColetadas" displayName="TabelaReviewsColetadas" ref="A1:M90" headerRowCount="1">
-  <autoFilter ref="A1:M90"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TabelaReviewsColetadas" displayName="TabelaReviewsColetadas" ref="A1:P90" headerRowCount="1">
+  <autoFilter ref="A1:P90"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="ASIN"/>
     <tableColumn id="2" name="SKU Base"/>
     <tableColumn id="3" name="SKU Anúncio"/>
     <tableColumn id="4" name="Produto"/>
     <tableColumn id="5" name="Título Amazon"/>
     <tableColumn id="6" name="Nome Avaliador"/>
-    <tableColumn id="7" name="Nota Review"/>
-    <tableColumn id="8" name="Título Review"/>
-    <tableColumn id="9" name="Data Review"/>
-    <tableColumn id="10" name="Compra Verificada"/>
-    <tableColumn id="11" name="Texto Review"/>
-    <tableColumn id="12" name="Review ID"/>
-    <tableColumn id="13" name="URL Fonte"/>
+    <tableColumn id="7" name="Status Nome"/>
+    <tableColumn id="8" name="Nome Bruto no HTML Amazon"/>
+    <tableColumn id="9" name="Perfil Avaliador URL"/>
+    <tableColumn id="10" name="Nota Review"/>
+    <tableColumn id="11" name="Título Review"/>
+    <tableColumn id="12" name="Data Review"/>
+    <tableColumn id="13" name="Compra Verificada"/>
+    <tableColumn id="14" name="Texto Review"/>
+    <tableColumn id="15" name="Review ID"/>
+    <tableColumn id="16" name="URL Fonte"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1"/>
 </table>
 </file>
 
@@ -516,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,14 +541,16 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,40 +606,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Nomes Válidos Extraídos</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Nomes Inválidos Filtrados</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>5 estrelas</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>4 estrelas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>3 estrelas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>2 estrelas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>1 estrela</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Status Página</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Status URL Reviews</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>URL Produto</t>
         </is>
@@ -677,27 +701,33 @@
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="n"/>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>200 len 0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>não consultada</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GSWLK5F3</t>
         </is>
@@ -749,27 +779,33 @@
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="2" t="n"/>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>não consultada</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>200 len 0</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GSWJ91JM</t>
         </is>
@@ -821,27 +857,33 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>não consultada</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GSWRMDRG</t>
         </is>
@@ -893,27 +935,33 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="2" t="n"/>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>200 len 2354</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>não consultada</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0DXWRQRQ4</t>
         </is>
@@ -965,27 +1013,33 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="2" t="n"/>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0DXWR7KDH</t>
         </is>
@@ -1037,27 +1091,33 @@
         <v>2</v>
       </c>
       <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>0.48</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n"/>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0DXX2LCRY</t>
         </is>
@@ -1109,27 +1169,33 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>0.62</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n"/>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>não consultada</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>200 len 0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0DY1XFQV6</t>
         </is>
@@ -1187,21 +1253,27 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="2" t="n"/>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB124QTV</t>
         </is>
@@ -1259,21 +1331,27 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="2" t="n"/>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB113GML</t>
         </is>
@@ -1325,27 +1403,33 @@
         <v>2</v>
       </c>
       <c r="K11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="2" t="n"/>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB15JQJS</t>
         </is>
@@ -1397,27 +1481,33 @@
         <v>6</v>
       </c>
       <c r="K12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="n">
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -1469,27 +1559,33 @@
         <v>1</v>
       </c>
       <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="2" t="n"/>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB12NYS1</t>
         </is>
@@ -1528,7 +1624,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
+          <t>2 de 5 estrelas</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1552,16 +1648,22 @@
       <c r="N14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="2" t="n"/>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTWK8G</t>
         </is>
@@ -1613,27 +1715,33 @@
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2" t="n"/>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB17CGD5</t>
         </is>
@@ -1685,27 +1793,33 @@
         <v>2</v>
       </c>
       <c r="K16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="n">
         <v>0.76</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n">
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB4RSKJY</t>
         </is>
@@ -1757,27 +1871,33 @@
         <v>2</v>
       </c>
       <c r="K17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="2" t="n"/>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3JWX7X2</t>
         </is>
@@ -1829,27 +1949,33 @@
         <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="2" t="n"/>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3JYHXYJ</t>
         </is>
@@ -1901,27 +2027,33 @@
         <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="M19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2" t="n"/>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZP5JMW</t>
         </is>
@@ -1973,27 +2105,33 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="2" t="n"/>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>200 len 0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>200 len 2354</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZG7MSH</t>
         </is>
@@ -2045,27 +2183,33 @@
         <v>2</v>
       </c>
       <c r="K21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="2" t="n"/>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB1523N3</t>
         </is>
@@ -2123,21 +2267,27 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="2" t="n"/>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZHCZ84</t>
         </is>
@@ -2189,27 +2339,33 @@
         <v>3</v>
       </c>
       <c r="K23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="2" t="n"/>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3PF22Y4</t>
         </is>
@@ -2261,27 +2417,33 @@
         <v>6</v>
       </c>
       <c r="K24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2" t="n">
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n">
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -2333,27 +2495,33 @@
         <v>6</v>
       </c>
       <c r="K25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2" t="n">
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n">
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -2405,27 +2573,33 @@
         <v>6</v>
       </c>
       <c r="K26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n">
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -2477,27 +2651,33 @@
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="2" t="n"/>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>200 len 2354</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>200 len 0</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GFPF42HC</t>
         </is>
@@ -2549,27 +2729,33 @@
         <v>0</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="N28" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="n"/>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>200 len 0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>não consultada</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G8RHLRFW</t>
         </is>
@@ -2621,27 +2807,33 @@
         <v>8</v>
       </c>
       <c r="K29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="N29" s="2" t="n">
         <v>0.12</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="O29" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>0.11</v>
       </c>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n">
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -2693,27 +2885,33 @@
         <v>3</v>
       </c>
       <c r="K30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="2" t="n"/>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GFPQD4G9</t>
         </is>
@@ -2765,27 +2963,33 @@
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="L31" s="2" t="n">
+      <c r="N31" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n"/>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTTMD4H</t>
         </is>
@@ -2837,27 +3041,33 @@
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="L32" s="2" t="n">
+      <c r="N32" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2" t="n"/>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTY2BLT</t>
         </is>
@@ -2909,27 +3119,33 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="L33" s="2" t="n">
+      <c r="N33" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="2" t="n"/>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTQ7YNR</t>
         </is>
@@ -2981,27 +3197,33 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="N34" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="2" t="n"/>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTVQQCJ</t>
         </is>
@@ -3053,27 +3275,33 @@
         <v>1</v>
       </c>
       <c r="K35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="N35" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2" t="n"/>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTL4HQ2</t>
         </is>
@@ -3125,27 +3353,33 @@
         <v>1</v>
       </c>
       <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="N36" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="M36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2" t="n"/>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTK2JL3</t>
         </is>
@@ -3197,27 +3431,33 @@
         <v>7</v>
       </c>
       <c r="K37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2" t="n">
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="P37" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n">
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -3269,27 +3509,33 @@
         <v>7</v>
       </c>
       <c r="K38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2" t="n">
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n">
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -3328,7 +3574,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,7 de 5 estrelas</t>
+          <t>4,9 de 5 estrelas</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -3352,16 +3598,22 @@
       <c r="N39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="2" t="n"/>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GWG2HL56</t>
         </is>
@@ -3424,16 +3676,22 @@
       <c r="N40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="2" t="n"/>
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GWS1151L</t>
         </is>
@@ -3485,27 +3743,33 @@
         <v>3</v>
       </c>
       <c r="K41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>0.71</v>
       </c>
-      <c r="L41" s="2" t="n">
+      <c r="N41" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="M41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="2" t="n"/>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>200 len 0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>200 len 2354</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G61FJG5S</t>
         </is>
@@ -3568,16 +3832,22 @@
       <c r="N42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="2" t="n"/>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G3R9RTBM</t>
         </is>
@@ -3629,27 +3899,33 @@
         <v>8</v>
       </c>
       <c r="K43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="L43" s="2" t="n">
+      <c r="N43" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="O43" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="N43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="T43" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -3701,27 +3977,33 @@
         <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="2" t="n"/>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>não consultada</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>200 len 0</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GQHJ9YCG</t>
         </is>
@@ -3784,16 +4066,22 @@
       <c r="N45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="2" t="n"/>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>200 len 0</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="T45" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GX7RN9FS</t>
         </is>
@@ -3810,8 +4098,13 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L45">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3828,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3837,13 +4130,16 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3879,35 +4175,50 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Status Nome</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Nome Bruto no HTML Amazon</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Perfil Avaliador URL</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Nota Review</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Título Review</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Data Review</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Compra Verificada</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Texto Review</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Review ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>URL Fonte</t>
         </is>
@@ -3939,34 +4250,53 @@
           <t>Jogo 7 Potes Vidro 520ml Marmita Hermético 800ml 1520ml</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>perfil público parece conter texto longo, não nome</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Excelente produto, superou minhas expectativas</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>4 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGXCHATBZUZL4X2A2KVQ45FOVRQQ</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 5 de janeiro de 2026</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>RXJX75IVDONUY</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>tampas não encaixam com facilidade mas são hermeticas</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-RXJX75IVDONUY</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0DXX2LCRY</t>
         </is>
@@ -4005,27 +4335,50 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Maura</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHE6CWDEX7RIZIZ76C4MOL6U24YQ</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>100% satisfeita</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 22 de maio de 2025</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>R27HQFAALLMAR6</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Muito bons! Ótimos Tamanhos, herméticos bem firmes, vidros de excelente qualidade. 100% satisfeita.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R27HQFAALLMAR6</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0DXX2LCRY</t>
         </is>
@@ -4064,27 +4417,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Eliane Lima</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AF4KAR75ON3Q4LA4C57VRS766CLQ</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Recomendo</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 1 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Excelente qualidade e pedido entregue no prazo. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>R2CV77ISSP9U2Q</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB124QTV</t>
         </is>
@@ -4123,35 +4499,50 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Potes de boa qualidade</t>
+          <t>Adriana Luisa Galasso Rossi</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHZ77Z2LDCADBEEWQZUWFQLB72NA</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Potes de boa qualidade</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 27 de julho de 2025</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Potes são de bom tamanho e com boa vedação. Valeu a compra. Ler mais</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R25DCXXQHVMH1O</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Potes são de bom tamanho e com boa vedação. Valeu a compra. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>R25DCXXQHVMH1O</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB113GML</t>
         </is>
@@ -4190,35 +4581,50 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Recomendo muito ótimo produto</t>
+          <t>Gi Martins</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHK6VF4SC4AWATJHSANJHC2BIH3A</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Recomendo muito ótimo produto</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 8 de setembro de 2025</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Amei amei amei, a melhor coisa que fiz foi comprar de tamanhos variados. Ótima vedação e tamanhos Ler mais</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-RAHFZNIFP9NRG</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Amei amei amei, a melhor coisa que fiz foi comprar de tamanhos variados. Ótima vedação e tamanhos Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>RAHFZNIFP9NRG</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB15JQJS</t>
         </is>
@@ -4257,35 +4663,50 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Potes</t>
+          <t>Zig</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AH7XHZP2CT35GHPMGUPTLTVY6SCA</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Potes</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 19 de julho de 2025</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Ótimo amei Ler mais</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R1JR9OV5DE3ZYW</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Ótimo amei Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>R1JR9OV5DE3ZYW</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB15JQJS</t>
         </is>
@@ -4324,27 +4745,50 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Charles Baptista Marques</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AERLR7JIQSBZJUDDSB3LO55CJKGQ</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 7 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Otimo Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>R16E6VHGVGXGAT</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -4383,27 +4827,50 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>monica</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AH33YKM3C75K3YLIPQ4HDXB2AAVA</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>lindo</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 1 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>muito bonito, entrega no prazo e bem embalado Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>R3SENU9ULDTK0N</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -4442,27 +4909,50 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFCPJ5V6QZUPMD4R6M63JT3BBDYA</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Produto quebrado</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 15 de julho de 2025</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Um produto veio quebrado! Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>RCRLB28YBMBIN</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -4501,27 +4991,50 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Esther</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHKL5UTENKWZWLL7WESZJHAMSOBQ</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 18 de julho de 2025</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Chegou rápido, bem embalado e exatamente igual ao anúncio. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>RJTOCFF11QSJ6</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -4560,27 +5073,50 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Amazon</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGUZDYBLMETQ5XWSCDDZFPABAZRA</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Vasilhas de vidro</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 26 de julho de 2025</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Gostei do tamanho e da qualidade Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>R3417N9SM58IVP</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -4612,34 +5148,53 @@
           <t>Kit 3 Potes Vidro Hermético Vedação Tampa 4 Travas Marmita</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>perfil público parece conter texto longo, não nome</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Super recomendo .... resolveu o problema de pontos "cegos" em minha casa. Produto sensacional ❗️❗️❗️👏👏👏👏👏</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AG43WGX5XEAC2XTT3ZEW3NGZHXZQ</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 2 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Excelente custo benefício Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>R3M8IEQWG49BBM</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZTX88N</t>
         </is>
@@ -4671,34 +5226,53 @@
           <t>Kit Jogo 6 Potes Vidro 640ml, 1050ml, 1520mlHermético Tampa Travas Marmita Fit</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>perfil público parece conter texto longo, não nome</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Literatura referente a conceito recente sobre a psicopatia humana e onde pessoas com essa psicopatia contagia inúmeras pessoas a ponto de modificar o pensamento de grande parcela da população e como as pessoas normais tem que conviver nesse novo contexto social adoentado.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEKBWW74V3MCFX5P2GZ2HT2UCHZA</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Resolve as necessidades dos marmiteiros.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 25 de janeiro de 2026</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Satisfaz as necessidades no armazenamento dos alimentos principalmente no transporte de marmitas e lanches na rotina externa no dia-a-dia. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>R2SI6K1N4R6CJI</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB12NYS1</t>
         </is>
@@ -4737,35 +5311,50 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,0 de 5 estrelas Bonitos e resistentes!</t>
+          <t>Maria Dolores</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHDCRPIULNWP6LUDF6L3MTJLA2GQ</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Bonitos e resistentes!</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 6 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Bonitos e resistentes! Mas muito pequenos! Ler mais</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-RKW93CWQTQ3YF</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Bonitos e resistentes! Mas muito pequenos! Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>RKW93CWQTQ3YF</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB17CGD5</t>
         </is>
@@ -4804,27 +5393,50 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Marina Medleg Simon</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AH6LO2WIWV422IBXCR2PL7CLST7A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Super prático</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 22 de dezembro de 2025</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Super prático e tamanho ótimo Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>R24YEM1UTBXR3N</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB4RSKJY</t>
         </is>
@@ -4863,27 +5475,50 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AERGN2MFCNGMQN4Q5TABCVCTDPVA</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Insatisfeito</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 28 de julho de 2025</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Os potes nao cumprem com o esperado, vazam o conteúdo. São bonitos e o material é resistente, porém nao trava como deveria. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>RUMMZ4WCEZGO7</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB4RSKJY</t>
         </is>
@@ -4922,35 +5557,50 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Elizabete Gonçalves de Aguiar</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGPHQ3GBGYJWHRZ6K35YW2EPLHZQ</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Produtos excelentes!</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Produtos excelentes!</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 28 de julho de 2025</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Amei o produto! Ler mais</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Amei o produto!</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>customer_review-R1DD32W02L6XVX</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3JWX7X2</t>
         </is>
@@ -4989,35 +5639,50 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Kindle</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGTI4JGYVPPHJUMJEVK5ZBGENMGQ</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Potede vidro com tampa hermética</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Potede vidro com tampa hermética</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 3 de junho de 2025</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Muito bom, atendeu perfeitamente minhas expectativas. Tem qualidade na tampa. Ler mais</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom, atendeu perfeitamente minhas expectativas. Tem qualidade na tampa.</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>customer_review-RMXL01C0YPAIX</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3JWX7X2</t>
         </is>
@@ -5056,27 +5721,50 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Rosy C.</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFPGFARNUISZGJBUCQWDEXDSCETA</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Excelente produto, perfeito…..</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 1 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>R34CNS2Q92HFJP</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Amei, veio tudo certo, bem embalado, excelente qualidade, vou comprar mais 🥰🥰🥰🥰🥰🤭🤭</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R34CNS2Q92HFJP</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3JYHXYJ</t>
         </is>
@@ -5115,27 +5803,50 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Ande da Soledade</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFU2SBQ2HFIPNPAXPD2W6PUWZLWA</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Conjunto de potes de vidro hermético</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 14 de junho de 2025</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>R2XA1CKLJETAOF</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Comprei dois kits para armazenar molhos, caldo de mandioca e outras comidinha. Meu congelador agora está super organizado e não preciso mais ficar abrindo os potes para ver o que tem dentro. Recomendo!</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2XA1CKLJETAOF</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3JYHXYJ</t>
         </is>
@@ -5174,35 +5885,50 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,0 de 5 estrelas Boa</t>
+          <t>PEDRO HENRIQUE MENDONÇA ALBUQUERQUE</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHPKFZ5RREUPZUQBIMIXHBLTD4SQ</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 5 de dezembro de 2025</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Muito bom, mas as vezes a tampa não fecha direito, pelo menos uma aba fica aberta Ler mais</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R1PNYV5QX93U8I</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom, mas as vezes a tampa não fecha direito, pelo menos uma aba fica aberta Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>R1PNYV5QX93U8I</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZP5JMW</t>
         </is>
@@ -5234,42 +5960,53 @@
           <t>Kit 4 Potes De Vidro 640ml Tampa Hermético 4 Travas Vedação</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>perfil público parece conter frase, não nome</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Maria Cecília Leite de Paiva Fernandes</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Potes de vidro</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWHJX3RHOIAYG2CF5OV2XVBP32Q</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Potes de vidro</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 17 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Perfeito ! Amei as peças ! Ler mais</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R2I63TY0UOAO53</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Perfeito ! Amei as peças ! Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>R2I63TY0UOAO53</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZG7MSH</t>
         </is>
@@ -5308,35 +6045,50 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Excelente</t>
+          <t>Marco Aurelio Migliorini Antunes</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AG3YXWTES6KX6AWBJZAQFYGW4HBQ</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 27 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>excelente perfeito Ler mais</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R3MOZ4WRE6JRPJ</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>excelente perfeito Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>R3MOZ4WRE6JRPJ</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB1523N3</t>
         </is>
@@ -5375,35 +6127,50 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Excelente</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEJTEFBCKPKDOGJPFFRJUKIRIBKA</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 14 de julho de 2025</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Excelente produto com qualidade e durabilidade. Ler mais</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-RBTRI9VNFAK8W</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Excelente produto com qualidade e durabilidade. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>RBTRI9VNFAK8W</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0FB1523N3</t>
         </is>
@@ -5442,35 +6209,50 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Maiara Luiza Feiten</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFAROSVFLTSBYJE27H7JTNBC2ZEQ</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Prático</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Prático</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 9 de outubro de 2025</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Muito bons. A borracha sai para lavar bem a tampa Ler mais</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Muito bons. A borracha sai para lavar bem a tampa</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>customer_review-R22V0B3EN1Z5T6</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F9ZHCZ84</t>
         </is>
@@ -5509,27 +6291,50 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Carlos A.</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFZQVQ35EAOUZOM2LQDHBFPIITXA</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Vale a pena!</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 27 de novembro de 2025</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>R1RZOUG2FR2N2L</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom, prático e de ótima qualidade!</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R1RZOUG2FR2N2L</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3PF22Y4</t>
         </is>
@@ -5568,27 +6373,50 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Kindle</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFYOI3NR7EZBUE4SCQ3PADWVC7LA</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Ótimo produto</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 11 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>R2MDBNJHCI4E35</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Excelente qualidade dos potes . Vale ressaltar o cuidado na embalagem do produto também. Recomendo a compra.</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2MDBNJHCI4E35</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3PF22Y4</t>
         </is>
@@ -5627,27 +6455,50 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Carla Danyelle</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEVYQSZCEFBM7DQ6H4FXWSZM2GEQ</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Marmita de vidro</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 16 de agosto de 2025</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>R160MK638WQK2N</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom, resistente e cabe bastante coisa, dar pra fazer lasanha também</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R160MK638WQK2N</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0F3PF22Y4</t>
         </is>
@@ -5686,27 +6537,50 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Nalu R M</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFQMCST32BYFARQJEGBXNTPRQV5A</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Cor e material perfeito.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 3 de maio de 2026</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Amei. Gosto de xicaras e canecas coloridas. O tamanho é perfeito. Serve como uma luva na cafeteira, sem ficar presa. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>R19VP34GOYWT15</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -5745,27 +6619,50 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Marco A. Campos</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHJ26DCDAWFORPDBLUMI4PYPLLIQ</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>3 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Parece ter boa qualidade</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 8 de maio de 2026</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Aparência ótima mas não tem 170 ml como na descrição, quero devolver e trocar por outra pouco maior Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>R1QA6FR2WX7X5J</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -5804,27 +6701,50 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AERI6UP7CTQSZZGFLSIGTKD7WCLQ</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>2 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Acabamento nem um pouco premium cheio de lascas na porcelana</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 24 de abril de 2026</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Produto veio muito bem embalado, mas cheio de defeitos. Lascas na parte de baixo, impossível que não tenham visto antes de enviar. Eu até não iria avaliar “mal”, mas na descrição diz acabamento “premium”: e não é, nem um pouco. Além disso, tem partes com uma tinta descolando (diferente da original), sugerindo que tentaram maquiar alguns defeitos. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>R19EN3HPIB1BQ0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -5863,27 +6783,50 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Mms</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFJ3ZNW57S6QUH4CAPFULPDUK3QA</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Ótimo produto.</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 5 de abril de 2026</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Gostei bastante. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>R33IY75HZ1XIW2</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -5922,27 +6865,50 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>adilson</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHJO4QVUP3FAW6NRNWME53HTSCLA</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Ótima compra</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 14 de março de 2026</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>São lindas, ótima qualidade. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>R2ZDIB4Y6Q9JE9</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -5981,27 +6947,50 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFJ7NWVADKH746G3O7IU64YD5Q4A</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Perfeitas</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 27 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Eu amei demais Comprarei novamente Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>RNMJYW95ORHLL</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGV3GW6H</t>
         </is>
@@ -6040,27 +7029,50 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Nalu R M</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFQMCST32BYFARQJEGBXNTPRQV5A</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Cor e material perfeito.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 3 de maio de 2026</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>R19VP34GOYWT15</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Amei. Gosto de xicaras e canecas coloridas. O tamanho é perfeito. Serve como uma luva na cafeteira, sem ficar presa.</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R19VP34GOYWT15</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -6099,27 +7111,50 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Marco A. Campos</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHJ26DCDAWFORPDBLUMI4PYPLLIQ</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>3,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Parece ter boa qualidade</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 8 de maio de 2026</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>R1QA6FR2WX7X5J</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Aparência ótima mas não tem 170 ml como na descrição, quero devolver e trocar por outra pouco maior</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R1QA6FR2WX7X5J</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -6158,27 +7193,50 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AERI6UP7CTQSZZGFLSIGTKD7WCLQ</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Acabamento nem um pouco premium cheio de lascas na porcelana</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 24 de abril de 2026</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>R19EN3HPIB1BQ0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Produto veio muito bem embalado, mas cheio de defeitos. Lascas na parte de baixo, impossível que não tenham visto antes de enviar. Eu até não iria avaliar “mal”, mas na descrição diz acabamento “premium”: e não é, nem um pouco. Além disso, tem partes com uma tinta descolando (diferente da original), sugerindo que tentaram maquiar alguns defeitos.</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R19EN3HPIB1BQ0</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -6217,27 +7275,50 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Mms</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFJ3ZNW57S6QUH4CAPFULPDUK3QA</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Ótimo produto.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 5 de abril de 2026</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>R33IY75HZ1XIW2</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Gostei bastante.</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R33IY75HZ1XIW2</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -6276,27 +7357,50 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>adilson</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHJO4QVUP3FAW6NRNWME53HTSCLA</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Ótima compra</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 14 de março de 2026</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>R2ZDIB4Y6Q9JE9</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>São lindas, ótima qualidade.</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2ZDIB4Y6Q9JE9</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -6335,27 +7439,50 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFJ7NWVADKH746G3O7IU64YD5Q4A</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Perfeitas</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 27 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>RNMJYW95ORHLL</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Eu amei demais Comprarei novamente</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-RNMJYW95ORHLL</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRQPRC</t>
         </is>
@@ -6394,35 +7521,50 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Nalu R M</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFQMCST32BYFARQJEGBXNTPRQV5A</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Cor e material perfeito.</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Cor e material perfeito.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 3 de maio de 2026</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Amei. Gosto de xicaras e canecas coloridas. O tamanho é perfeito. Serve como uma luva na cafeteira, sem ficar presa. Ler mais</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Amei. Gosto de xicaras e canecas coloridas. O tamanho é perfeito. Serve como uma luva na cafeteira, sem ficar presa.</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>customer_review-R19VP34GOYWT15</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -6461,35 +7603,50 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Marco A. Campos</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHJ26DCDAWFORPDBLUMI4PYPLLIQ</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>3,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>3,0 de 5 estrelas Parece ter boa qualidade</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Parece ter boa qualidade</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 8 de maio de 2026</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Aparência ótima mas não tem 170 ml como na descrição, quero devolver e trocar por outra pouco maior Ler mais</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Aparência ótima mas não tem 170 ml como na descrição, quero devolver e trocar por outra pouco maior</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>customer_review-R1QA6FR2WX7X5J</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -6528,35 +7685,50 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AERI6UP7CTQSZZGFLSIGTKD7WCLQ</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>2,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2,0 de 5 estrelas Acabamento nem um pouco premium cheio de lascas na porcelana</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Acabamento nem um pouco premium cheio de lascas na porcelana</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 24 de abril de 2026</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Produto veio muito bem embalado, mas cheio de defeitos. Lascas na parte de baixo, impossível que não tenham visto antes de enviar. Eu até não iria avaliar “mal”, mas na descrição diz acabamento “premium”: e não é, nem um pouco. Além disso, tem partes com uma tinta descolando (diferente da original), sugerindo que tentaram maquiar alguns defeitos. Ler mais</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Produto veio muito bem embalado, mas cheio de defeitos. Lascas na parte de baixo, impossível que não tenham visto antes de enviar. Eu até não iria avaliar “mal”, mas na descrição diz acabamento “premium”: e não é, nem um pouco. Além disso, tem partes com uma tinta descolando (diferente da original), sugerindo que tentaram maquiar alguns defeitos.</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>customer_review-R19EN3HPIB1BQ0</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -6595,35 +7767,50 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Mms</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFJ3ZNW57S6QUH4CAPFULPDUK3QA</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Ótimo produto.</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Ótimo produto.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 5 de abril de 2026</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Gostei bastante. Ler mais</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Gostei bastante.</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>customer_review-R33IY75HZ1XIW2</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -6662,35 +7849,50 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>adilson</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHJO4QVUP3FAW6NRNWME53HTSCLA</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Ótima compra</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Ótima compra</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 14 de março de 2026</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>São lindas, ótima qualidade. Ler mais</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>São lindas, ótima qualidade.</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>customer_review-R2ZDIB4Y6Q9JE9</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -6729,35 +7931,50 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFJ7NWVADKH746G3O7IU64YD5Q4A</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Perfeitas</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Perfeitas</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 27 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Eu amei demais Comprarei novamente Ler mais</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Eu amei demais Comprarei novamente</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>customer_review-RNMJYW95ORHLL</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTRYN4Q</t>
         </is>
@@ -6796,23 +8013,46 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Kindle</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFPE34JQALSYIUZB344GRO6MDZDA</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Excelente qualidade</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Lindas! Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>R1VD90F4Z0WO5Q</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GFPF42HC</t>
         </is>
@@ -6851,35 +8091,50 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Qualidade</t>
+          <t>Priscila Amorim Bezerra dos Santos</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AECQEY73DHRSEZFX2TSGSSYUAILQ</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 22 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Lindo, faz muito sucesso aqui em casa, atendeu totalmente o q preciso. Ler mais</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R23YR1H7R0K2RP</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Lindo, faz muito sucesso aqui em casa, atendeu totalmente o q preciso. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>R23YR1H7R0K2RP</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -6918,35 +8173,50 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Bonito para decorar</t>
+          <t>Lais</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEIHPHOO2WVDRLEYPF5G74STEO4Q</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Bonito para decorar</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 31 de março de 2026</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>O suporte de madeira não vem envernizado. Mas é bonitinho para decoração. Ler mais</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-ROUZTKBNOXTJJ</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>O suporte de madeira não vem envernizado. Mas é bonitinho para decoração. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ROUZTKBNOXTJJ</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -6985,35 +8255,50 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,0 de 5 estrelas Só serve pra enfeite!</t>
+          <t>katiuscia</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHXBGCLT4KASQSB6Q3GG7W3N52LQ</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>2 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Só serve pra enfeite!</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 25 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>São lindas mas só pra enfeite! Não presta pra tomar café! Esquenta muuuuito! Se não tiver cuidado queimam a boca e a mão! Não me atendeu. Ler mais</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R3EUDORMH071VL</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>São lindas mas só pra enfeite! Não presta pra tomar café! Esquenta muuuuito! Se não tiver cuidado queimam a boca e a mão! Não me atendeu. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>R3EUDORMH071VL</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -7052,35 +8337,50 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,0 de 5 estrelas Pessimo !</t>
+          <t>elizeth senna</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEMVU55CNS5D7VUFVW3QOAFI4SRQ</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>1 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Pessimo !</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 18 de março de 2026</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>A mídia não pôde ser carregada. Produto de pessimamente qualidade! Pintura duvidosa, material ruim, suporte muito mal feito, mal acabado! Não recomendo! Vou ver como é a devolução! Ler mais</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R2Z1Q77KMT2TF9</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Produto de pessimamente qualidade! Pintura duvidosa, material ruim, suporte muito mal feito, mal acabado! Não recomendo! Vou ver como é a devolução! Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>R2Z1Q77KMT2TF9</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -7119,35 +8419,50 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>3,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,0 de 5 estrelas Esquentam muito :(</t>
+          <t>…</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGXHSVTTJLMW2YPJMIJ6AJMMIREA</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>3 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Esquentam muito :(</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 18 de janeiro de 2026</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>São lindas, mas esquentam muito e fica impossível tomar café quentinho. Fica muito quente pra pegar e ao encostar na boca. Mas para quem não toma café muito quente, deve valer a pena! Pois são lindas :) Ler mais</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R2BOZROIX57XMP</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>São lindas, mas esquentam muito e fica impossível tomar café quentinho. Fica muito quente pra pegar e ao encostar na boca. Mas para quem não toma café muito quente, deve valer a pena! Pois são lindas :) Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>R2BOZROIX57XMP</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -7186,35 +8501,50 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Boas</t>
+          <t>Maria jolinda botelho ruas</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AENF4IXMOTJCWDXR7BWIPO4XA2RQ</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Boas</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 31 de dezembro de 2025</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Lindinhas,porem minusculas Ler mais</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R1SJQ4493RK2S4</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Lindinhas,porem minusculas Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>R1SJQ4493RK2S4</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -7253,35 +8583,50 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,0 de 5 estrelas Não vale</t>
+          <t>Fabiana Almirante</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AF24WGM2GTHMFHLTZSECQ6JFEBDA</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>1 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Não vale</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 27 de abril de 2026</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Péssima qualidade Ler mais</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R3KVMO4VB4V22X</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Péssima qualidade Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>R3KVMO4VB4V22X</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -7320,35 +8665,50 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>3,0 de 5 estrelas Esquenta nas asas</t>
+          <t>Albaniza do Nascimento Werkauser</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AE3TN2QVQPZCEI76SDXAPACLEBGA</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>3 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Esquenta nas asas</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 12 de janeiro de 2026</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Lindas. Mas esquenta muito nas asas Ler mais</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R2DD4KPK7GSVAP</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Lindas. Mas esquenta muito nas asas Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>R2DD4KPK7GSVAP</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2SV7NR1</t>
         </is>
@@ -7387,27 +8747,50 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Neusa Benedetti</t>
+        </is>
+      </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFZQIGSNQXATX2WGO6XIRUUFS6FA</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Canecas bonitas. Não sei se resistentes.</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 18 de março de 2026</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>R2VL5WFTLR44Y1</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Canecas muito bonitas e boas!! Só que Vieram duas canecas com a alça quebrada.</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2VL5WFTLR44Y1</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GFPQD4G9</t>
         </is>
@@ -7446,27 +8829,50 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Super maravilhoso 5 ⭐</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGNAOH64FX4JDKZDSJNOF6JY653A</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>1,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Chegou assim</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 28 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>R1XQ2F8UZZRWR5</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Quebrados</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R1XQ2F8UZZRWR5</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GFPQD4G9</t>
         </is>
@@ -7505,27 +8911,50 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFKK5PCWHM65JRQQWNNZQSPGEBCQ</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>1,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Péssima qualidade veio quebradas</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 20 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>R2AM5W6ENCKIS1</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>A mídia não pôde ser carregada. Infelizmente são xicaras de péssima qualidade e ja vinheram quebradas e outras ja estao soltando da alça.</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2AM5W6ENCKIS1</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GFPQD4G9</t>
         </is>
@@ -7564,27 +8993,50 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Valéria</t>
+        </is>
+      </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWXI4BGHH3MN6HO3A6MICYMIA3Q</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Ótimas canecas</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>R2A0FQ5NCW6FP6</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador.</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2A0FQ5NCW6FP6</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTTMD4H</t>
         </is>
@@ -7623,35 +9075,50 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Valéria</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWXI4BGHH3MN6HO3A6MICYMIA3Q</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Ótimas canecas</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Ótimas canecas</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador.</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>customer_review-R2A0FQ5NCW6FP6</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="P61" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTY2BLT</t>
         </is>
@@ -7690,35 +9157,50 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Ótimas canecas</t>
+          <t>Valéria</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWXI4BGHH3MN6HO3A6MICYMIA3Q</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Ótimas canecas</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R2A0FQ5NCW6FP6</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>R2A0FQ5NCW6FP6</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTQ7YNR</t>
         </is>
@@ -7757,27 +9239,50 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Valéria</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWXI4BGHH3MN6HO3A6MICYMIA3Q</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Ótimas canecas</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>R2A0FQ5NCW6FP6</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTVQQCJ</t>
         </is>
@@ -7816,27 +9321,50 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Valéria</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWXI4BGHH3MN6HO3A6MICYMIA3Q</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Ótimas canecas</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>R2A0FQ5NCW6FP6</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTL4HQ2</t>
         </is>
@@ -7875,35 +9403,50 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5,0 de 5 estrelas Ótimas canecas</t>
+          <t>Valéria</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHWXI4BGHH3MN6HO3A6MICYMIA3Q</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>5 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Ótimas canecas</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>customer_review-R2A0FQ5NCW6FP6</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>As canecas são ótimas, bonitas e vieram cuidadosamente embaladas… e ainda bem, já que a caixa maior onde estavam acondicionadas com outro produto que comprei, foi jogada pelo muro do prédio pelo entregador. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>R2A0FQ5NCW6FP6</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GGTK2JL3</t>
         </is>
@@ -7942,35 +9485,50 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Marcos Antônio Viana Soares</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFHZGTTV4AROHDXIMZEDCTLJ46ZA</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Aprovado</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 25 de abril de 2026</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Muito bom, aprovado. Ler mais</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom, aprovado.</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>customer_review-R3IOOBO1YPWZWD</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="P66" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8009,35 +9567,50 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Camila Gimenes</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEMV6SZCNM55PVR62HGCG36R5X3A</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
           <t>1,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>1,0 de 5 estrelas Produto péssimo</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Produto péssimo</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 14 de março de 2026</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Não gostei do produto as peças de encaixe são bem maiores que o buraco pra em caixar e veio faltando peças. Ler mais</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Não gostei do produto as peças de encaixe são bem maiores que o buraco pra em caixar e veio faltando peças.</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>customer_review-RI7Y1ZGS97II9</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="P67" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8076,35 +9649,50 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Nascimento</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFM66TK65U3OLKU5HYJWGXM6WSTA</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
           <t>2,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>2,0 de 5 estrelas Muito fraco</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Muito fraco</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 8 de maio de 2026</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Suporte simples e bem fraquinho Ler mais</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Suporte simples e bem fraquinho</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>customer_review-R1U7OG2BLIBY3V</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8143,35 +9731,50 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Danny Daniel</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEIJH3CIYOTMAA34NU3UKGPMNKYA</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
           <t>3,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>3,0 de 5 estrelas Simples e compacto</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Simples e compacto</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 30 de abril de 2026</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>A construção é interessante e bem simples, apenas encaixando as peças você consegue usar, porém notei que é simples demais os encaixes, o que pode sair com o tempo, logo já coloquei os elásticos que vieram no produto para não sair, nesse aspecto, precisa melhorar no encaixe e transmitir mais segurança. Ler mais</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>A construção é interessante e bem simples, apenas encaixando as peças você consegue usar, porém notei que é simples demais os encaixes, o que pode sair com o tempo, logo já coloquei os elásticos que vieram no produto para não sair, nesse aspecto, precisa melhorar no encaixe e transmitir mais segurança.</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>customer_review-R19CY4UG38DHXP</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="P69" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8210,35 +9813,50 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFPE7VDC3D27KJMGFXAVVM764WEA</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Excelente produto</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Excelente produto</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 16 de março de 2026</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Gostei demais desse suporte, chegou em apenas 1 dia, veio bem embalado também Ler mais</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Gostei demais desse suporte, chegou em apenas 1 dia, veio bem embalado também</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>customer_review-R2HKKV135HK937</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8277,35 +9895,50 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>guilherme</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFTYWHAIZQ6QKPMOEUXQ2UVJRD5Q</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
           <t>1,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>1,0 de 5 estrelas Legal, mas não funcional</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Legal, mas não funcional</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 30 de abril de 2026</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>.... Ler mais</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>....</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>customer_review-R9G69OQUPU5EF</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="P71" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8344,35 +9977,50 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Luís Fernando Oliveira dos Santos</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AF2GIDM2QJYM7X6HYE5BR2TCSH5Q</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
           <t>1,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>1,0 de 5 estrelas Suporte</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 5 de maio de 2026</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Produto de madeira. Má qualidade Ler mais</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Produto de madeira. Má qualidade</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>customer_review-R3M3GLCLE6SOWQ</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GH2BTQFJ</t>
         </is>
@@ -8411,27 +10059,50 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Marcos Antônio Viana Soares</t>
+        </is>
+      </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFHZGTTV4AROHDXIMZEDCTLJ46ZA</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 25 de abril de 2026</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>R3IOOBO1YPWZWD</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Muito bom, aprovado.</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R3IOOBO1YPWZWD</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8470,27 +10141,50 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Camila Gimenes</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEMV6SZCNM55PVR62HGCG36R5X3A</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>1,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Produto péssimo</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 14 de março de 2026</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>RI7Y1ZGS97II9</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Não gostei do produto as peças de encaixe são bem maiores que o buraco pra em caixar e veio faltando peças.</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-RI7Y1ZGS97II9</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8529,27 +10223,50 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Nascimento</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFM66TK65U3OLKU5HYJWGXM6WSTA</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>2,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Muito fraco</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 8 de maio de 2026</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>R1U7OG2BLIBY3V</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Suporte simples e bem fraquinho</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R1U7OG2BLIBY3V</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8588,27 +10305,50 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>3 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Danny Daniel</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEIJH3CIYOTMAA34NU3UKGPMNKYA</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>3,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Simples e compacto</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 30 de abril de 2026</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>R19CY4UG38DHXP</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>A construção é interessante e bem simples, apenas encaixando as peças você consegue usar, porém notei que é simples demais os encaixes, o que pode sair com o tempo, logo já coloquei os elásticos que vieram no produto para não sair, nesse aspecto, precisa melhorar no encaixe e transmitir mais segurança.</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R19CY4UG38DHXP</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8647,27 +10387,50 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>5 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFPE7VDC3D27KJMGFXAVVM764WEA</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>5,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Excelente produto</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 16 de março de 2026</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>R2HKKV135HK937</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Gostei demais desse suporte, chegou em apenas 1 dia, veio bem embalado também</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R2HKKV135HK937</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8706,27 +10469,50 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>guilherme</t>
+        </is>
+      </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFTYWHAIZQ6QKPMOEUXQ2UVJRD5Q</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>1,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Legal, mas não funcional</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 30 de abril de 2026</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>R9G69OQUPU5EF</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>....</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R9G69OQUPU5EF</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8765,27 +10551,50 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1 de 5 estrelas</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Luís Fernando Oliveira dos Santos</t>
+        </is>
+      </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AF2GIDM2QJYM7X6HYE5BR2TCSH5Q</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>1,0 de 5 estrelas</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
           <t>Avaliado no Brasil em 5 de maio de 2026</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>R3M3GLCLE6SOWQ</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Produto de madeira. Má qualidade</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>customer_review-R3M3GLCLE6SOWQ</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0GTQXRDTM</t>
         </is>
@@ -8824,27 +10633,50 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEAU5ZFANHB3UDSZYOAGVFWYISCA</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Saco plastico</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 12 de abril de 2026</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Boa qualidade Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>R1NJQ8PMJR2K4T</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="P80" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G61FJG5S</t>
         </is>
@@ -8883,27 +10715,50 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>larissa m</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AFTQ3S2OXXWDZWXN364VEY4MUCLA</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
           <t>4 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>É bem grande</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 4 de março de 2026</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Eu achei que fosse aqueles sacos menores pra congelar. Ele é bem grande, não prestei atenção. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>R2FJHNC0YG4S3I</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="P81" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G61FJG5S</t>
         </is>
@@ -8942,27 +10797,50 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Zani</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AELTQU3J43YWE37UIOUACE2UPGYQ</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
           <t>5 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Processo e produto aprovados.</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 2 de abril de 2026</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>O produto é de boa qualidade; veio bem embalado; a entrega foi rápida e sem problemas. Ler mais Ler menos</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>R296NY85QOCGUB</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="P82" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G61FJG5S</t>
         </is>
@@ -9001,35 +10879,50 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>VAMILZA DE FONTES OLIVEIRA CORDEIRO</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AH4SNO4JH235OYLOX2HH7XAYXKKQ</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas QUALIDADE INCRÍVEL</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>QUALIDADE INCRÍVEL</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 28 de abril de 2026</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>A jarra é linda, vidro bem grosso, tamanho ideal, super recomendo. Ler mais</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>A jarra é linda, vidro bem grosso, tamanho ideal, super recomendo.</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>customer_review-R2QD6R7XIXAHEU</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9068,35 +10961,50 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Janine</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHXRFNU6XZQIZWCJTZXXK7SPDV2A</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Jarra muito bonita</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Jarra muito bonita</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 22 de abril de 2026</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Adorei a qualidade do produto. Bonito e resistente. Chegou rápido e muito bem embalado. Fiquei muito satisfeita com a minha compra. Recomendo. Ler mais</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Adorei a qualidade do produto. Bonito e resistente. Chegou rápido e muito bem embalado. Fiquei muito satisfeita com a minha compra. Recomendo.</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>customer_review-R1PQYU7JDSIIT6</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="P84" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9135,35 +11043,50 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Pitzer Milton</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGFILZ4KMJA6BCPZBWDRWHS6HC4A</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Produto robusto, com indicação muito clara das medidas, como anunciado.</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Produto robusto, com indicação muito clara das medidas, como anunciado.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 28 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Produto ótimo e muito adequado ao fim a que sestina. Como destaque, recomendo a compra, pois, tenho outro, de outra marca famosa, mas o bico entorna sempre fora do ponto e escorre, o que NÃO ocorre com este modelo comprado. Ler mais</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Produto ótimo e muito adequado ao fim a que sestina. Como destaque, recomendo a compra, pois, tenho outro, de outra marca famosa, mas o bico entorna sempre fora do ponto e escorre, o que NÃO ocorre com este modelo comprado.</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>customer_review-RERR77RJXNNPW</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9202,35 +11125,50 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Ana Carolina Rodrigues Batista</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEHRQOBKLFR4QDZGVWC3NCVVMSQA</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Produto ótimo</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Produto ótimo</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 21 de abril de 2026</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Super bem embalado! Adorei o produto, pesado e lindo Ler mais</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Super bem embalado! Adorei o produto, pesado e lindo</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>customer_review-ROC5OPLYBFZL1</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9269,35 +11207,50 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Cliente Amazon</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AGFWLVE5N6E3EYF2IFWFKRY3TPUQ</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Ótimo!</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Ótimo!</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 30 de abril de 2026</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Tamanho perfeito! Ler mais</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Tamanho perfeito!</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>customer_review-R110AVDIBA266C</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9336,35 +11289,50 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>MÁRCIA SOUZA DA SILVA GONCALVES</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AHMKLTXRAAJLQ6XRQF4LOAAJROEQ</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
           <t>4,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>4,0 de 5 estrelas Resistente</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Resistente</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 25 de fevereiro de 2026</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Veio bem embalado, aparentemente é bem resistente. Pecou um pouquinho na escrita, está um pouco apagada. Ler mais</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Veio bem embalado, aparentemente é bem resistente. Pecou um pouquinho na escrita, está um pouco apagada.</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>customer_review-R11005DUCPBV8E</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="P88" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9403,35 +11371,50 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Antonia Xavier</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AH3IOFQVMV3KJL7BXWVDUPDKOACA</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas É lindo! Gostei muito.</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>É lindo! Gostei muito.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 13 de abril de 2026</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Produto ótimo, bem embalado. Recomendo Ler mais</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Produto ótimo, bem embalado. Recomendo</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>customer_review-R3DVYJDAGAZLGF</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="P89" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9470,35 +11453,50 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Ingrid Estrella</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/gp/profile/amzn1.account.AEPPOUQYCPCUJIO22H6RSCIJC7LA</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
           <t>5,0 de 5 estrelas</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>5,0 de 5 estrelas Otimo</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Otimo</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>Avaliado no Brasil em 4 de maio de 2026</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>Compra verificada</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Ótima qualidade, bico que não vaza. Veio bem embalado Ler mais</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Ótima qualidade, bico que não vaza. Veio bem embalado</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>customer_review-R3SETTD7P00ZND</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="P90" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/dp/B0G2CWWMGK</t>
         </is>
@@ -9518,11 +11516,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9545,7 +11543,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 15:14 UTC</t>
+          <t>2026-05-12 15:57 UTC</t>
         </is>
       </c>
     </row>
@@ -9594,7 +11592,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Total reviews com nome extraído</t>
+          <t>Total reviews públicas extraídas</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -9604,24 +11602,44 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Limitação importante</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon SP-API não expõe nome do avaliador; nomes só entram quando publicados no HTML público. Classificações sem texto não têm nome público associado.</t>
-        </is>
+          <t>Nomes válidos extraídos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Método</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>ASINs canônicos da planilha Amazon + páginas públicas Amazon BR via Bright Data Web Unlocker.</t>
+          <t>Nomes filtrados por parecerem texto de review/frase</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Correção de auditoria</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Nome Avaliador agora só recebe valores curtos/person-like. Quando o HTML público da Amazon traz frase/texto no campo de perfil, o valor é preservado em Nome Bruto no HTML Amazon e o Nome Avaliador fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Limitação importante</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Amazon SP-API não expõe nome do avaliador; nomes só entram quando publicados no HTML público. Classificações sem texto não têm nome público associado.</t>
         </is>
       </c>
     </row>

--- a/exports/amazon-avaliacoes-budamix-2026-05-12.xlsx
+++ b/exports/amazon-avaliacoes-budamix-2026-05-12.xlsx
@@ -2339,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>

--- a/exports/amazon-avaliacoes-budamix-2026-05-12.xlsx
+++ b/exports/amazon-avaliacoes-budamix-2026-05-12.xlsx
@@ -2105,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -5960,10 +5960,14 @@
           <t>Kit 4 Potes De Vidro 640ml Tampa Hermético 4 Travas Vedação</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Maria Cecília Leite de Paiva Fernandes</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>perfil público parece conter frase, não nome</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -11606,7 +11610,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -11616,7 +11620,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
